--- a/data/trans_camb/P16A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,31</t>
+          <t>0,54; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,11</t>
+          <t>-1,24; 4,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,81</t>
+          <t>-1,87; 3,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,3</t>
+          <t>-2,68; 6,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,5</t>
+          <t>-4,27; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,12</t>
+          <t>-6,84; 0,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,72</t>
+          <t>0,08; 5,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,33</t>
+          <t>-1,83; 3,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,86</t>
+          <t>-3,46; 0,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 667,1</t>
+          <t>-12,63; 563,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 391,47</t>
+          <t>-46,09; 383,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 241,53</t>
+          <t>-61,03; 259,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 139,53</t>
+          <t>-31,14; 159,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 106,52</t>
+          <t>-48,7; 99,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,26; 7,81</t>
+          <t>-70,03; 12,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 174,68</t>
+          <t>0,06; 195,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 109,3</t>
+          <t>-33,05; 102,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 29,04</t>
+          <t>-58,12; 27,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,43</t>
+          <t>-1,02; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,89</t>
+          <t>-1,25; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,72</t>
+          <t>1,21; 6,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,15</t>
+          <t>-1,54; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,72</t>
+          <t>-2,82; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,84</t>
+          <t>0,07; 6,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,64</t>
+          <t>-0,52; 3,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,73</t>
+          <t>-1,15; 2,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,6</t>
+          <t>1,42; 5,44</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 280,56</t>
+          <t>-40,97; 260,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 221,04</t>
+          <t>-39,09; 198,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 455,17</t>
+          <t>25,07; 458,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 105,4</t>
+          <t>-19,63; 110,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 72,19</t>
+          <t>-33,94; 67,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 116,03</t>
+          <t>-0,05; 126,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 103,59</t>
+          <t>-10,9; 102,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 75,81</t>
+          <t>-21,87; 76,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,65; 166,66</t>
+          <t>26,05; 152,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,06</t>
+          <t>-0,86; 5,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,01</t>
+          <t>-1,15; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,36</t>
+          <t>-0,0; 5,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,56</t>
+          <t>0,66; 4,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,11</t>
+          <t>3,1; 8,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,77</t>
+          <t>5,47; 9,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,83</t>
+          <t>0,44; 3,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,43</t>
+          <t>1,62; 5,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,16</t>
+          <t>3,3; 6,81</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 507,05</t>
+          <t>-45,51; 627,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 488,05</t>
+          <t>-54,3; 431,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 567,72</t>
+          <t>-9,46; 578,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 638,81</t>
+          <t>16,05; 702,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91,92; 946,07</t>
+          <t>70,73; 856,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>159,05; 1391,7</t>
+          <t>177,49; 1315,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,37</t>
+          <t>-0,91; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,84</t>
+          <t>0,78; 5,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,95</t>
+          <t>-0,82; 3,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,85</t>
+          <t>2,9; 9,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,12</t>
+          <t>0,98; 8,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,83</t>
+          <t>-3,5; 1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,1</t>
+          <t>1,69; 5,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,18</t>
+          <t>1,78; 5,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,98</t>
+          <t>-1,51; 1,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 672,85</t>
+          <t>-56,81; 790,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 1059,95</t>
+          <t>-1,89; 1342,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 752,7</t>
+          <t>-61,28; 937,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45,7; 345,24</t>
+          <t>50,62; 400,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,38; 334,09</t>
+          <t>13,27; 322,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 69,98</t>
+          <t>-61,15; 82,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,31; 328,13</t>
+          <t>47,23; 317,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,94; 332,57</t>
+          <t>46,91; 331,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 105,15</t>
+          <t>-43,92; 101,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,57</t>
+          <t>-1,33; 5,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,73</t>
+          <t>-0,87; 5,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,96</t>
+          <t>-2,22; 2,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 16,94</t>
+          <t>4,38; 16,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 13,47</t>
+          <t>1,42; 12,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 8,55</t>
+          <t>0,13; 8,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,18</t>
+          <t>2,62; 9,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,36</t>
+          <t>1,64; 8,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,11</t>
+          <t>0,13; 5,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 645,38</t>
+          <t>-57,67; 555,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 494,33</t>
+          <t>-39,58; 557,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 389,36</t>
+          <t>-65,53; 344,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42,57; 506,17</t>
+          <t>43,53; 430,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,19; 353,33</t>
+          <t>11,13; 351,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,02; 274,67</t>
+          <t>-0,71; 256,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,28; 347,01</t>
+          <t>40,3; 331,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24,31; 303,33</t>
+          <t>25,35; 284,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 183,21</t>
+          <t>0,13; 197,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,09</t>
+          <t>0,02; 4,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,39</t>
+          <t>0,36; 5,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,98</t>
+          <t>2,33; 7,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,68</t>
+          <t>-1,35; 5,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,53</t>
+          <t>-1,15; 5,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,95</t>
+          <t>3,87; 10,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,1</t>
+          <t>0,11; 4,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,31</t>
+          <t>0,21; 4,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,05</t>
+          <t>3,77; 8,11</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,98; —</t>
+          <t>-50,72; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,82; —</t>
+          <t>-21,79; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55,4; —</t>
+          <t>83,84; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 333,71</t>
+          <t>-34,26; 281,34</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 334,5</t>
+          <t>-30,54; 285,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,8; 654,82</t>
+          <t>64,39; 598,54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 310,0</t>
+          <t>-3,09; 328,47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,67; 337,32</t>
+          <t>2,72; 387,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>111,48; 667,99</t>
+          <t>120,37; 741,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,32</t>
+          <t>-1,4; 2,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,98</t>
+          <t>-0,9; 2,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,91</t>
+          <t>-0,83; 3,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,55</t>
+          <t>-3,25; 1,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,92</t>
+          <t>-0,52; 4,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,1</t>
+          <t>-2,31; 5,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,23</t>
+          <t>-1,79; 1,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,33</t>
+          <t>-0,22; 3,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,53</t>
+          <t>-0,74; 3,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 129,12</t>
+          <t>-42,44; 146,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 170,03</t>
+          <t>-30,26; 175,92</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 165,63</t>
+          <t>-23,67; 185,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 45,23</t>
+          <t>-51,34; 36,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 130,68</t>
+          <t>-9,8; 130,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 116,3</t>
+          <t>-37,92; 120,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 40,94</t>
+          <t>-39,13; 43,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 105,11</t>
+          <t>-5,42; 94,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 108,23</t>
+          <t>-13,89; 105,18</t>
         </is>
       </c>
     </row>
@@ -2189,32 +2189,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,33</t>
+          <t>-3,72; 0,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,83</t>
+          <t>-3,4; 0,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,86</t>
+          <t>-3,81; 1,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,16</t>
+          <t>-3,04; 2,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,4</t>
+          <t>-2,17; 3,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,65</t>
+          <t>0,59; 6,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,64</t>
+          <t>-1,95; 1,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,01</t>
+          <t>-2,11; 3,1</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 9,73</t>
+          <t>-66,47; 15,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 26,42</t>
+          <t>-58,16; 17,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 46,76</t>
+          <t>-62,88; 47,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 34,97</t>
+          <t>-34,97; 34,41</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 52,51</t>
+          <t>-24,07; 55,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,17; 105,89</t>
+          <t>5,29; 115,58</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 14,35</t>
+          <t>-39,98; 12,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 31,92</t>
+          <t>-27,72; 30,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 54,45</t>
+          <t>-31,6; 56,23</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,67</t>
+          <t>-0,03; 1,64</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,8</t>
+          <t>0,11; 1,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,53</t>
+          <t>0,49; 2,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,86</t>
+          <t>0,56; 2,99</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,55</t>
+          <t>1,14; 3,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,79</t>
+          <t>1,1; 3,89</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,07</t>
+          <t>0,58; 2,11</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,36</t>
+          <t>0,91; 2,4</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,94</t>
+          <t>1,11; 2,92</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 77,42</t>
+          <t>-2,94; 75,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4,03; 81,07</t>
+          <t>2,09; 82,39</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13,21; 112,3</t>
+          <t>18,27; 108,79</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10,35; 58,08</t>
+          <t>10,3; 62,99</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,88; 74,19</t>
+          <t>20,46; 74,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>19,05; 79,45</t>
+          <t>18,63; 81,67</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,69; 56,02</t>
+          <t>13,68; 57,31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>21,77; 65,12</t>
+          <t>21,25; 67,13</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>28,13; 81,43</t>
+          <t>27,45; 80,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,86</t>
+          <t>0,89; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,27</t>
+          <t>-1,13; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,03</t>
+          <t>-2,03; 2,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 6,5</t>
+          <t>-3,11; 6,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 4,76</t>
+          <t>-4,73; 4,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,33</t>
+          <t>-6,91; 0,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,92</t>
+          <t>0,17; 6,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,39</t>
+          <t>-2,03; 3,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,86</t>
+          <t>-3,52; 0,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,41%</t>
+          <t>-46,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,68%</t>
+          <t>-29,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 563,12</t>
+          <t>18,68; 689,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 383,82</t>
+          <t>-42,84; 433,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 259,0</t>
+          <t>-61,5; 255,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 159,52</t>
+          <t>-37,04; 145,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 99,4</t>
+          <t>-50,89; 90,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,03; 12,7</t>
+          <t>-70,16; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 195,5</t>
+          <t>0,26; 183,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 102,56</t>
+          <t>-36,59; 91,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 27,52</t>
+          <t>-58,85; 21,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,99</t>
+          <t>-0,89; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,99</t>
+          <t>-1,35; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,68</t>
+          <t>1,54; 6,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,26</t>
+          <t>-1,59; 5,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,39</t>
+          <t>-2,79; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,28</t>
+          <t>0,04; 5,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,84</t>
+          <t>-0,28; 3,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,81</t>
+          <t>-1,17; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,44</t>
+          <t>1,35; 5,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156,23%</t>
+          <t>153,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 260,75</t>
+          <t>-32,29; 292,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 198,0</t>
+          <t>-40,53; 216,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,07; 458,58</t>
+          <t>33,78; 412,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 110,67</t>
+          <t>-21,43; 100,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 67,2</t>
+          <t>-34,71; 75,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 126,72</t>
+          <t>-0,37; 116,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 102,18</t>
+          <t>-6,94; 98,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 76,55</t>
+          <t>-21,34; 68,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 152,14</t>
+          <t>23,28; 143,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,17</t>
+          <t>-0,68; 5,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,76</t>
+          <t>-1,22; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,28</t>
+          <t>0,14; 5,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,23</t>
+          <t>0,64; 4,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,09</t>
+          <t>3,23; 8,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,99</t>
+          <t>5,35; 9,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,81</t>
+          <t>0,55; 3,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,22</t>
+          <t>1,8; 5,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,81</t>
+          <t>3,53; 6,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140,92%</t>
+          <t>135,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2689,84%</t>
+          <t>2657,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>481,37%</t>
+          <t>474,0%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 627,92</t>
+          <t>-46,09; 467,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 431,83</t>
+          <t>-51,15; 428,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 578,12</t>
+          <t>-5,21; 551,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 702,67</t>
+          <t>21,57; 633,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70,73; 856,37</t>
+          <t>94,5; 984,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177,49; 1315,51</t>
+          <t>160,63; 1225,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,59</t>
+          <t>-0,8; 3,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,55</t>
+          <t>0,79; 5,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,83</t>
+          <t>-0,79; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,91</t>
+          <t>2,8; 9,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,56</t>
+          <t>1,2; 8,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,92</t>
+          <t>-2,43; 2,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,79</t>
+          <t>1,71; 6,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,96</t>
+          <t>1,69; 5,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,92</t>
+          <t>-0,96; 2,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,64%</t>
+          <t>-0,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 790,26</t>
+          <t>-59,99; 754,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1342,08</t>
+          <t>4,19; 1423,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 937,17</t>
+          <t>-65,37; 753,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,62; 400,12</t>
+          <t>45,66; 368,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,27; 322,88</t>
+          <t>13,39; 307,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 82,9</t>
+          <t>-45,36; 106,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,23; 317,89</t>
+          <t>38,71; 335,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,91; 331,24</t>
+          <t>42,11; 324,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 101,08</t>
+          <t>-28,88; 124,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,5</t>
+          <t>-1,48; 5,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,76</t>
+          <t>-1,0; 6,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,93</t>
+          <t>-2,59; 2,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 16,17</t>
+          <t>4,09; 16,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,95</t>
+          <t>1,87; 13,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,25</t>
+          <t>-0,09; 8,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,56</t>
+          <t>2,67; 9,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,08</t>
+          <t>1,37; 7,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,29</t>
+          <t>-0,26; 4,81</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 555,55</t>
+          <t>-50,85; 609,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 557,06</t>
+          <t>-39,58; 662,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 344,12</t>
+          <t>-73,17; 269,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43,53; 430,7</t>
+          <t>40,31; 428,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,13; 351,26</t>
+          <t>12,91; 332,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 256,24</t>
+          <t>-3,89; 243,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,3; 331,18</t>
+          <t>39,52; 354,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>25,35; 284,37</t>
+          <t>18,03; 266,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,13; 197,29</t>
+          <t>-6,23; 184,51</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>5,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,35</t>
+          <t>0,08; 4,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,57</t>
+          <t>0,4; 5,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,2</t>
+          <t>2,13; 6,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,87</t>
+          <t>-1,11; 5,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,53</t>
+          <t>-1,12; 5,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,83</t>
+          <t>4,03; 10,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,09</t>
+          <t>0,01; 4,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,62</t>
+          <t>0,26; 4,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,11</t>
+          <t>3,85; 7,9</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>640,35%</t>
+          <t>620,25%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>228,07%</t>
+          <t>224,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>293,42%</t>
+          <t>288,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,72; —</t>
+          <t>-43,59; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,79; —</t>
+          <t>-42,89; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>83,84; —</t>
+          <t>79,94; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 281,34</t>
+          <t>-33,52; 286,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 285,23</t>
+          <t>-32,13; 311,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,39; 598,54</t>
+          <t>68,44; 576,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 328,47</t>
+          <t>-6,41; 304,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,72; 387,85</t>
+          <t>1,44; 379,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>120,37; 741,05</t>
+          <t>114,44; 698,2</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,53</t>
+          <t>-1,38; 2,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,88</t>
+          <t>-1,03; 2,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,21</t>
+          <t>-0,87; 3,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,41</t>
+          <t>-3,42; 1,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,92</t>
+          <t>-0,28; 4,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,24</t>
+          <t>1,38; 6,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,37</t>
+          <t>-1,67; 1,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,04</t>
+          <t>-0,14; 3,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,4</t>
+          <t>1,02; 4,24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 146,42</t>
+          <t>-42,88; 138,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 175,92</t>
+          <t>-30,88; 175,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 185,7</t>
+          <t>-29,27; 192,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 36,67</t>
+          <t>-52,54; 35,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 130,56</t>
+          <t>-5,76; 127,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 120,29</t>
+          <t>21,89; 172,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 43,75</t>
+          <t>-37,48; 38,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 94,01</t>
+          <t>-4,66; 105,73</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 105,18</t>
+          <t>20,81; 134,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,29</t>
+          <t>-3,76; -0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,58</t>
+          <t>-3,32; 0,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,84</t>
+          <t>-1,45; 2,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,19</t>
+          <t>-3,35; 2,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,38</t>
+          <t>-2,08; 3,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,66</t>
+          <t>-0,15; 5,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,61</t>
+          <t>-2,81; 0,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,55</t>
+          <t>-2,03; 1,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,1</t>
+          <t>-0,03; 3,35</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-12,42%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 15,59</t>
+          <t>-68,58; 4,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 17,16</t>
+          <t>-58,1; 17,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 47,17</t>
+          <t>-27,8; 80,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 34,41</t>
+          <t>-36,62; 31,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 55,13</t>
+          <t>-24,52; 54,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,29; 115,58</t>
+          <t>-1,71; 81,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 12,18</t>
+          <t>-39,53; 12,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 30,22</t>
+          <t>-29,46; 28,93</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 56,23</t>
+          <t>-0,61; 64,16</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,64</t>
+          <t>-0,14; 1,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,79</t>
+          <t>0,12; 1,76</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,45</t>
+          <t>0,8; 2,52</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,99</t>
+          <t>0,54; 2,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,52</t>
+          <t>1,09; 3,53</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,89</t>
+          <t>1,94; 4,12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,59; 2,11</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,4</t>
+          <t>0,91; 2,34</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,92</t>
+          <t>1,74; 3,13</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 75,01</t>
+          <t>-5,31; 72,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,09; 82,39</t>
+          <t>3,01; 81,56</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18,27; 108,79</t>
+          <t>25,63; 115,25</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10,3; 62,99</t>
+          <t>8,32; 60,61</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,46; 74,39</t>
+          <t>17,47; 72,34</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,63; 81,67</t>
+          <t>32,69; 85,97</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,68; 57,31</t>
+          <t>12,89; 56,63</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>21,25; 67,13</t>
+          <t>20,4; 63,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>27,45; 80,19</t>
+          <t>40,09; 86,95</t>
         </is>
       </c>
     </row>
